--- a/Data/EXCEL/Transfer/salemon/20240711/6877-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6877-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F67E626-7EE0-4417-BFF0-E16333C919C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9BCB65-B2F1-4415-9E8A-B79CC2A0CD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{682C8592-AEB3-4900-BE1E-91A001C04695}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{6B754E3A-6A2E-499C-834A-967EBD1FC764}"/>
   </bookViews>
   <sheets>
     <sheet name="6877-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,23 +1261,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6050AF2-FC40-4EA5-8CA3-D2AE0543A7A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{379D942F-1DA2-4780-9367-00B608C45BD9}">
   <dimension ref="A1:Q70"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1304,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1386,7 +1386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1425,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>-2.59</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>-7.96</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>-2.33</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>-8.3800000000000008</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>-3.75</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>-1.53</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>148.80000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>-5.72</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>-3.51</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>-56.3</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>-36.200000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>42.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3121,172 +3121,172 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>44501</v>
       </c>
